--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD51D60-49FD-4E1B-BE71-B8647E93FEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2116FBCF-D1B0-4EF7-9D47-6B31D7980D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70303,8 +70303,8 @@
       <c r="D482" s="52" t="s">
         <v>472</v>
       </c>
-      <c r="E482" s="53">
-        <v>11400010</v>
+      <c r="E482" s="14">
+        <v>1140003</v>
       </c>
       <c r="F482" s="14">
         <v>30031</v>
@@ -70415,8 +70415,8 @@
       <c r="D483" s="52" t="s">
         <v>473</v>
       </c>
-      <c r="E483" s="53">
-        <v>11400010</v>
+      <c r="E483" s="14">
+        <v>1140003</v>
       </c>
       <c r="F483" s="14">
         <v>30031</v>
@@ -70527,8 +70527,8 @@
       <c r="D484" s="52" t="s">
         <v>474</v>
       </c>
-      <c r="E484" s="53">
-        <v>11400010</v>
+      <c r="E484" s="14">
+        <v>1140003</v>
       </c>
       <c r="F484" s="14">
         <v>30031</v>
@@ -70639,8 +70639,8 @@
       <c r="D485" s="52" t="s">
         <v>475</v>
       </c>
-      <c r="E485" s="53">
-        <v>11400010</v>
+      <c r="E485" s="14">
+        <v>1140003</v>
       </c>
       <c r="F485" s="14">
         <v>30031</v>
@@ -70751,8 +70751,8 @@
       <c r="D486" s="52" t="s">
         <v>476</v>
       </c>
-      <c r="E486" s="53">
-        <v>11400010</v>
+      <c r="E486" s="14">
+        <v>1140003</v>
       </c>
       <c r="F486" s="14">
         <v>30031</v>
@@ -70863,8 +70863,8 @@
       <c r="D487" s="52" t="s">
         <v>478</v>
       </c>
-      <c r="E487" s="53">
-        <v>11400010</v>
+      <c r="E487" s="14">
+        <v>1140003</v>
       </c>
       <c r="F487" s="14">
         <v>30031</v>
@@ -70975,8 +70975,8 @@
       <c r="D488" s="52" t="s">
         <v>479</v>
       </c>
-      <c r="E488" s="53">
-        <v>11400010</v>
+      <c r="E488" s="14">
+        <v>1140003</v>
       </c>
       <c r="F488" s="14">
         <v>30031</v>
@@ -71087,8 +71087,8 @@
       <c r="D489" s="52" t="s">
         <v>480</v>
       </c>
-      <c r="E489" s="53">
-        <v>11400010</v>
+      <c r="E489" s="14">
+        <v>1140003</v>
       </c>
       <c r="F489" s="14">
         <v>30031</v>
@@ -71199,8 +71199,8 @@
       <c r="D490" s="52" t="s">
         <v>481</v>
       </c>
-      <c r="E490" s="53">
-        <v>11400010</v>
+      <c r="E490" s="14">
+        <v>1140003</v>
       </c>
       <c r="F490" s="14">
         <v>30031</v>
@@ -71311,8 +71311,8 @@
       <c r="D491" s="52" t="s">
         <v>482</v>
       </c>
-      <c r="E491" s="53">
-        <v>11400010</v>
+      <c r="E491" s="14">
+        <v>1140003</v>
       </c>
       <c r="F491" s="14">
         <v>30031</v>
@@ -71423,8 +71423,8 @@
       <c r="D492" s="52" t="s">
         <v>483</v>
       </c>
-      <c r="E492" s="53">
-        <v>11400010</v>
+      <c r="E492" s="14">
+        <v>1140003</v>
       </c>
       <c r="F492" s="14">
         <v>30031</v>
@@ -71535,8 +71535,8 @@
       <c r="D493" s="52" t="s">
         <v>484</v>
       </c>
-      <c r="E493" s="53">
-        <v>11400010</v>
+      <c r="E493" s="14">
+        <v>1140003</v>
       </c>
       <c r="F493" s="14">
         <v>30031</v>
